--- a/input/faculty_combined_input.xlsx
+++ b/input/faculty_combined_input.xlsx
@@ -5,17 +5,30 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed3544907b8a3db/Desktop/ai agents_vu_faculty/input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed3544907b8a3db/Desktop/AI-faculty-course-allocation-main(2)/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_681D91BBD380551DA1A2CAF0505ED87656CD0853" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26654E99-7B0F-4DED-B99C-F3168B23C504}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_681D91BBD380551DA1A2CAF0505ED87656CD0853" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49C6FDF5-31D1-481C-8003-5CDC7E59038A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -559,8 +572,11 @@
   <cols>
     <col min="1" max="1" width="20.36328125" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="17.6328125" customWidth="1"/>
     <col min="6" max="6" width="18.1796875" customWidth="1"/>
+    <col min="12" max="12" width="19.81640625" customWidth="1"/>
+    <col min="13" max="13" width="30.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
